--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -4604,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117430089</v>
+        <v>117491133</v>
       </c>
       <c r="B38" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,30 +4616,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4647,10 +4656,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490039</v>
+        <v>490105</v>
       </c>
       <c r="R38" t="n">
-        <v>6931761</v>
+        <v>6931938</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4710,10 +4719,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117430507</v>
+        <v>117430545</v>
       </c>
       <c r="B39" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4722,30 +4731,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4753,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490007</v>
+        <v>490044</v>
       </c>
       <c r="R39" t="n">
-        <v>6931806</v>
+        <v>6931836</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4922,10 +4936,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117430545</v>
+        <v>117430089</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4934,35 +4948,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4970,10 +4979,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490044</v>
+        <v>490039</v>
       </c>
       <c r="R41" t="n">
-        <v>6931836</v>
+        <v>6931761</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5033,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117491133</v>
+        <v>117430507</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5045,39 +5054,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490105</v>
+        <v>490007</v>
       </c>
       <c r="R42" t="n">
-        <v>6931938</v>
+        <v>6931806</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117492320</v>
+        <v>117429691</v>
       </c>
       <c r="B43" t="n">
-        <v>79562</v>
+        <v>97836</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5160,30 +5160,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5191,10 +5200,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490085</v>
+        <v>490021</v>
       </c>
       <c r="R43" t="n">
-        <v>6931971</v>
+        <v>6931639</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,10 +5263,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117429691</v>
+        <v>117492320</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>79562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5266,39 +5275,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490021</v>
+        <v>490085</v>
       </c>
       <c r="R44" t="n">
-        <v>6931639</v>
+        <v>6931971</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117429822</v>
+        <v>117492202</v>
       </c>
       <c r="B15" t="n">
-        <v>97857</v>
+        <v>78514</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,31 +2127,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2159,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490056</v>
+        <v>490061</v>
       </c>
       <c r="R15" t="n">
-        <v>6931648</v>
+        <v>6931865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117492369</v>
+        <v>117430040</v>
       </c>
       <c r="B16" t="n">
-        <v>79562</v>
+        <v>79521</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490067</v>
+        <v>490060</v>
       </c>
       <c r="R16" t="n">
-        <v>6931971</v>
+        <v>6931682</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117430056</v>
+        <v>117491453</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2340,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490061</v>
+        <v>490096</v>
       </c>
       <c r="R17" t="n">
-        <v>6931684</v>
+        <v>6931958</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117492202</v>
+        <v>117430408</v>
       </c>
       <c r="B18" t="n">
-        <v>78514</v>
+        <v>79561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2450,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2477,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490061</v>
+        <v>490012</v>
       </c>
       <c r="R18" t="n">
-        <v>6931865</v>
+        <v>6931800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,6 +2512,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2540,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117429793</v>
+        <v>117492153</v>
       </c>
       <c r="B19" t="n">
-        <v>94240</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,29 +2556,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2584,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490021</v>
+        <v>490067</v>
       </c>
       <c r="R19" t="n">
-        <v>6931643</v>
+        <v>6931856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117430719</v>
+        <v>117492238</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,39 +2671,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2699,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490137</v>
+        <v>490070</v>
       </c>
       <c r="R20" t="n">
-        <v>6931927</v>
+        <v>6931876</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,6 +2738,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117492336</v>
+        <v>117430089</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>78514</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2778,21 +2786,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2805,10 +2813,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490087</v>
+        <v>490039</v>
       </c>
       <c r="R21" t="n">
-        <v>6931968</v>
+        <v>6931761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,10 +2876,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117429852</v>
+        <v>117429822</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>97857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2880,30 +2888,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2914,7 +2923,7 @@
         <v>490056</v>
       </c>
       <c r="R22" t="n">
-        <v>6931671</v>
+        <v>6931648</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2974,10 +2983,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117430761</v>
+        <v>117430507</v>
       </c>
       <c r="B23" t="n">
-        <v>79561</v>
+        <v>78514</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,21 +2999,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3017,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490117</v>
+        <v>490007</v>
       </c>
       <c r="R23" t="n">
-        <v>6931912</v>
+        <v>6931806</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117492355</v>
+        <v>117430761</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,31 +3101,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3124,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490067</v>
+        <v>490117</v>
       </c>
       <c r="R24" t="n">
-        <v>6931971</v>
+        <v>6931912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3187,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117492153</v>
+        <v>117430056</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>79590</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3199,39 +3207,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3239,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490067</v>
+        <v>490061</v>
       </c>
       <c r="R25" t="n">
-        <v>6931856</v>
+        <v>6931684</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3302,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117430743</v>
+        <v>117430446</v>
       </c>
       <c r="B26" t="n">
-        <v>74584</v>
+        <v>104914</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,30 +3313,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490130</v>
+        <v>489965</v>
       </c>
       <c r="R26" t="n">
-        <v>6931907</v>
+        <v>6931782</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117430446</v>
+        <v>117430545</v>
       </c>
       <c r="B27" t="n">
-        <v>104914</v>
+        <v>97836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,28 +3420,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489965</v>
+        <v>490044</v>
       </c>
       <c r="R27" t="n">
-        <v>6931782</v>
+        <v>6931836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3621,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117491453</v>
+        <v>117491486</v>
       </c>
       <c r="B29" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,30 +3637,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3664,10 +3677,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490096</v>
+        <v>490063</v>
       </c>
       <c r="R29" t="n">
-        <v>6931958</v>
+        <v>6931903</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117491096</v>
+        <v>117491191</v>
       </c>
       <c r="B30" t="n">
-        <v>79596</v>
+        <v>79561</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,10 +3783,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490055</v>
+        <v>490084</v>
       </c>
       <c r="R30" t="n">
-        <v>6931974</v>
+        <v>6931897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3806,6 +3819,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3833,10 +3851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117491078</v>
+        <v>117491116</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3845,39 +3863,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3885,10 +3894,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490048</v>
+        <v>490055</v>
       </c>
       <c r="R31" t="n">
-        <v>6931976</v>
+        <v>6931974</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3948,10 +3957,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117491191</v>
+        <v>117430608</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>90517</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3964,21 +3973,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3991,10 +4000,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490084</v>
+        <v>489984</v>
       </c>
       <c r="R32" t="n">
-        <v>6931897</v>
+        <v>6931792</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4027,11 +4036,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117430588</v>
+        <v>117429691</v>
       </c>
       <c r="B33" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4071,30 +4075,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4102,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490018</v>
+        <v>490021</v>
       </c>
       <c r="R33" t="n">
-        <v>6931884</v>
+        <v>6931639</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4165,10 +4178,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117430632</v>
+        <v>117492369</v>
       </c>
       <c r="B34" t="n">
-        <v>97857</v>
+        <v>79562</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4177,31 +4190,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4209,10 +4221,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489989</v>
+        <v>490067</v>
       </c>
       <c r="R34" t="n">
-        <v>6931777</v>
+        <v>6931971</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,10 +4284,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117491116</v>
+        <v>117492355</v>
       </c>
       <c r="B35" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4284,30 +4296,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4315,10 +4328,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490055</v>
+        <v>490067</v>
       </c>
       <c r="R35" t="n">
-        <v>6931974</v>
+        <v>6931971</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4391,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117430408</v>
+        <v>117491078</v>
       </c>
       <c r="B36" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4390,30 +4403,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4421,10 +4443,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490012</v>
+        <v>490048</v>
       </c>
       <c r="R36" t="n">
-        <v>6931800</v>
+        <v>6931976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,11 +4479,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4489,10 +4506,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117491486</v>
+        <v>117430730</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4501,39 +4518,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4541,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490063</v>
+        <v>490132</v>
       </c>
       <c r="R37" t="n">
-        <v>6931903</v>
+        <v>6931915</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,10 +4612,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117491133</v>
+        <v>117492484</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,39 +4624,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4656,10 +4655,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490105</v>
+        <v>490068</v>
       </c>
       <c r="R38" t="n">
-        <v>6931938</v>
+        <v>6931975</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4719,10 +4718,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117430545</v>
+        <v>117430485</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>94240</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4731,32 +4730,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490044</v>
+        <v>489966</v>
       </c>
       <c r="R39" t="n">
-        <v>6931836</v>
+        <v>6931786</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4830,10 +4825,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117430114</v>
+        <v>117429793</v>
       </c>
       <c r="B40" t="n">
-        <v>79561</v>
+        <v>94240</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4842,30 +4837,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4873,10 +4869,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490047</v>
+        <v>490021</v>
       </c>
       <c r="R40" t="n">
-        <v>6931770</v>
+        <v>6931643</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4936,7 +4932,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117430089</v>
+        <v>117492308</v>
       </c>
       <c r="B41" t="n">
         <v>78514</v>
@@ -4979,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490039</v>
+        <v>490076</v>
       </c>
       <c r="R41" t="n">
-        <v>6931761</v>
+        <v>6931894</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5042,10 +5038,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117430507</v>
+        <v>117492257</v>
       </c>
       <c r="B42" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5054,30 +5050,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5085,10 +5090,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490007</v>
+        <v>490070</v>
       </c>
       <c r="R42" t="n">
-        <v>6931806</v>
+        <v>6931897</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5148,10 +5153,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117429691</v>
+        <v>117492336</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5160,39 +5165,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5200,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490021</v>
+        <v>490087</v>
       </c>
       <c r="R43" t="n">
-        <v>6931639</v>
+        <v>6931968</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5263,10 +5259,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117492320</v>
+        <v>117429852</v>
       </c>
       <c r="B44" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5279,21 +5275,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5306,10 +5302,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490085</v>
+        <v>490056</v>
       </c>
       <c r="R44" t="n">
-        <v>6931971</v>
+        <v>6931671</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5369,10 +5365,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117491148</v>
+        <v>117430114</v>
       </c>
       <c r="B45" t="n">
-        <v>90464</v>
+        <v>79561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5381,25 +5377,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5412,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490106</v>
+        <v>490047</v>
       </c>
       <c r="R45" t="n">
-        <v>6931918</v>
+        <v>6931770</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,10 +5471,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117492308</v>
+        <v>117430743</v>
       </c>
       <c r="B46" t="n">
-        <v>78514</v>
+        <v>74584</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5491,21 +5487,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5518,10 +5514,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490076</v>
+        <v>490130</v>
       </c>
       <c r="R46" t="n">
-        <v>6931894</v>
+        <v>6931907</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5581,10 +5577,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117492238</v>
+        <v>117430588</v>
       </c>
       <c r="B47" t="n">
-        <v>79561</v>
+        <v>78514</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5597,21 +5593,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5624,10 +5620,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490070</v>
+        <v>490018</v>
       </c>
       <c r="R47" t="n">
-        <v>6931876</v>
+        <v>6931884</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5660,11 +5656,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,10 +5683,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117430040</v>
+        <v>117430632</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>97857</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,26 +5699,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5735,10 +5727,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490060</v>
+        <v>489989</v>
       </c>
       <c r="R48" t="n">
-        <v>6931682</v>
+        <v>6931777</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5798,7 +5790,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117492257</v>
+        <v>117491133</v>
       </c>
       <c r="B49" t="n">
         <v>97836</v>
@@ -5833,7 +5825,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5850,10 +5842,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490070</v>
+        <v>490105</v>
       </c>
       <c r="R49" t="n">
-        <v>6931897</v>
+        <v>6931938</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5913,10 +5905,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117430608</v>
+        <v>117491148</v>
       </c>
       <c r="B50" t="n">
-        <v>90517</v>
+        <v>90464</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5925,25 +5917,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5956,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489984</v>
+        <v>490106</v>
       </c>
       <c r="R50" t="n">
-        <v>6931792</v>
+        <v>6931918</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6019,10 +6011,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117430730</v>
+        <v>117491096</v>
       </c>
       <c r="B51" t="n">
-        <v>79561</v>
+        <v>79596</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6031,25 +6023,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6062,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490132</v>
+        <v>490055</v>
       </c>
       <c r="R51" t="n">
-        <v>6931915</v>
+        <v>6931974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6125,10 +6117,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117430485</v>
+        <v>117430719</v>
       </c>
       <c r="B52" t="n">
-        <v>94240</v>
+        <v>97836</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6137,29 +6129,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489966</v>
+        <v>490137</v>
       </c>
       <c r="R52" t="n">
-        <v>6931786</v>
+        <v>6931927</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117492484</v>
+        <v>117492320</v>
       </c>
       <c r="B53" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6248,21 +6248,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490068</v>
+        <v>490085</v>
       </c>
       <c r="R53" t="n">
-        <v>6931975</v>
+        <v>6931971</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117492202</v>
+        <v>117430545</v>
       </c>
       <c r="B15" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,30 +2127,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490061</v>
+        <v>490044</v>
       </c>
       <c r="R15" t="n">
-        <v>6931865</v>
+        <v>6931836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117430040</v>
+        <v>117430507</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>78516</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2238,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490060</v>
+        <v>490007</v>
       </c>
       <c r="R16" t="n">
-        <v>6931682</v>
+        <v>6931806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117491453</v>
+        <v>117430761</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490096</v>
+        <v>490117</v>
       </c>
       <c r="R17" t="n">
-        <v>6931958</v>
+        <v>6931912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2438,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117430408</v>
+        <v>117492369</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2454,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490012</v>
+        <v>490067</v>
       </c>
       <c r="R18" t="n">
-        <v>6931800</v>
+        <v>6931971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,11 +2517,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117492153</v>
+        <v>117491096</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>79598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,39 +2556,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490067</v>
+        <v>490055</v>
       </c>
       <c r="R19" t="n">
-        <v>6931856</v>
+        <v>6931974</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117492238</v>
+        <v>117430446</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>104916</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,30 +2662,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2702,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490070</v>
+        <v>489965</v>
       </c>
       <c r="R20" t="n">
-        <v>6931876</v>
+        <v>6931782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,11 +2730,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,10 +2757,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117430089</v>
+        <v>117430408</v>
       </c>
       <c r="B21" t="n">
-        <v>78514</v>
+        <v>79563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,21 +2773,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2813,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490039</v>
+        <v>490012</v>
       </c>
       <c r="R21" t="n">
-        <v>6931761</v>
+        <v>6931800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,6 +2836,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117429822</v>
+        <v>117430588</v>
       </c>
       <c r="B22" t="n">
-        <v>97857</v>
+        <v>78516</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2888,31 +2880,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2920,10 +2911,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490056</v>
+        <v>490018</v>
       </c>
       <c r="R22" t="n">
-        <v>6931648</v>
+        <v>6931884</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,10 +2974,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117430507</v>
+        <v>117430730</v>
       </c>
       <c r="B23" t="n">
-        <v>78514</v>
+        <v>79563</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,21 +2990,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3026,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490007</v>
+        <v>490132</v>
       </c>
       <c r="R23" t="n">
-        <v>6931806</v>
+        <v>6931915</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117430761</v>
+        <v>117492320</v>
       </c>
       <c r="B24" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,21 +3096,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3132,10 +3123,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490117</v>
+        <v>490085</v>
       </c>
       <c r="R24" t="n">
-        <v>6931912</v>
+        <v>6931971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3195,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117430056</v>
+        <v>117491078</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,30 +3198,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490061</v>
+        <v>490048</v>
       </c>
       <c r="R25" t="n">
-        <v>6931684</v>
+        <v>6931976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117430446</v>
+        <v>117429852</v>
       </c>
       <c r="B26" t="n">
-        <v>104914</v>
+        <v>79563</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3313,31 +3313,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3345,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489965</v>
+        <v>490056</v>
       </c>
       <c r="R26" t="n">
-        <v>6931782</v>
+        <v>6931671</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3408,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117430545</v>
+        <v>117430056</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>79592</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,35 +3419,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3456,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490044</v>
+        <v>490061</v>
       </c>
       <c r="R27" t="n">
-        <v>6931836</v>
+        <v>6931684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3519,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117492397</v>
+        <v>117492257</v>
       </c>
       <c r="B28" t="n">
-        <v>79596</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,30 +3525,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3565,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490067</v>
+        <v>490070</v>
       </c>
       <c r="R28" t="n">
-        <v>6931971</v>
+        <v>6931897</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3625,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117491486</v>
+        <v>117491453</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3637,39 +3640,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3677,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490063</v>
+        <v>490096</v>
       </c>
       <c r="R29" t="n">
-        <v>6931903</v>
+        <v>6931958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117491191</v>
+        <v>117491486</v>
       </c>
       <c r="B30" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,30 +3746,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3783,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490084</v>
+        <v>490063</v>
       </c>
       <c r="R30" t="n">
-        <v>6931897</v>
+        <v>6931903</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,11 +3822,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3851,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117491116</v>
+        <v>117492153</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3863,30 +3861,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3894,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490055</v>
+        <v>490067</v>
       </c>
       <c r="R31" t="n">
-        <v>6931974</v>
+        <v>6931856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3957,10 +3964,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117430608</v>
+        <v>117491191</v>
       </c>
       <c r="B32" t="n">
-        <v>90517</v>
+        <v>79563</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3973,21 +3980,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,10 +4007,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489984</v>
+        <v>490084</v>
       </c>
       <c r="R32" t="n">
-        <v>6931792</v>
+        <v>6931897</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,6 +4043,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,10 +4075,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117429691</v>
+        <v>117492238</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4075,39 +4087,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4115,10 +4118,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490021</v>
+        <v>490070</v>
       </c>
       <c r="R33" t="n">
-        <v>6931639</v>
+        <v>6931876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,6 +4154,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4178,10 +4186,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117492369</v>
+        <v>117429793</v>
       </c>
       <c r="B34" t="n">
-        <v>79562</v>
+        <v>94242</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4190,30 +4198,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4221,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490067</v>
+        <v>490021</v>
       </c>
       <c r="R34" t="n">
-        <v>6931971</v>
+        <v>6931643</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4284,10 +4293,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117492355</v>
+        <v>117430719</v>
       </c>
       <c r="B35" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4317,8 +4326,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4328,10 +4345,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490067</v>
+        <v>490137</v>
       </c>
       <c r="R35" t="n">
-        <v>6931971</v>
+        <v>6931927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4391,10 +4408,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117491078</v>
+        <v>117491148</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>90466</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4403,39 +4420,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4443,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490048</v>
+        <v>490106</v>
       </c>
       <c r="R36" t="n">
-        <v>6931976</v>
+        <v>6931918</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4506,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117430730</v>
+        <v>117492202</v>
       </c>
       <c r="B37" t="n">
-        <v>79561</v>
+        <v>78516</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4522,21 +4530,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4557,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490132</v>
+        <v>490061</v>
       </c>
       <c r="R37" t="n">
-        <v>6931915</v>
+        <v>6931865</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4612,10 +4620,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117492484</v>
+        <v>117430040</v>
       </c>
       <c r="B38" t="n">
-        <v>79561</v>
+        <v>79523</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4624,25 +4632,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4655,10 +4663,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490068</v>
+        <v>490060</v>
       </c>
       <c r="R38" t="n">
-        <v>6931975</v>
+        <v>6931682</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4718,10 +4726,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117430485</v>
+        <v>117491133</v>
       </c>
       <c r="B39" t="n">
-        <v>94240</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4730,29 +4738,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4762,10 +4778,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489966</v>
+        <v>490105</v>
       </c>
       <c r="R39" t="n">
-        <v>6931786</v>
+        <v>6931938</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4825,10 +4841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117429793</v>
+        <v>117430114</v>
       </c>
       <c r="B40" t="n">
-        <v>94240</v>
+        <v>79563</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4837,31 +4853,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4869,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490021</v>
+        <v>490047</v>
       </c>
       <c r="R40" t="n">
-        <v>6931643</v>
+        <v>6931770</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4932,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117492308</v>
+        <v>117492336</v>
       </c>
       <c r="B41" t="n">
-        <v>78514</v>
+        <v>79563</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4948,21 +4963,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4975,10 +4990,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490076</v>
+        <v>490087</v>
       </c>
       <c r="R41" t="n">
-        <v>6931894</v>
+        <v>6931968</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5038,10 +5053,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117492257</v>
+        <v>117429691</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5073,7 +5088,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5090,10 +5105,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490070</v>
+        <v>490021</v>
       </c>
       <c r="R42" t="n">
-        <v>6931897</v>
+        <v>6931639</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5153,10 +5168,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117492336</v>
+        <v>117430632</v>
       </c>
       <c r="B43" t="n">
-        <v>79561</v>
+        <v>97859</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5165,30 +5180,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5196,10 +5212,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490087</v>
+        <v>489989</v>
       </c>
       <c r="R43" t="n">
-        <v>6931968</v>
+        <v>6931777</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5259,10 +5275,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117429852</v>
+        <v>117430608</v>
       </c>
       <c r="B44" t="n">
-        <v>79561</v>
+        <v>90519</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5275,21 +5291,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5302,10 +5318,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490056</v>
+        <v>489984</v>
       </c>
       <c r="R44" t="n">
-        <v>6931671</v>
+        <v>6931792</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5365,10 +5381,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117430114</v>
+        <v>117492484</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5408,10 +5424,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490047</v>
+        <v>490068</v>
       </c>
       <c r="R45" t="n">
-        <v>6931770</v>
+        <v>6931975</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5471,10 +5487,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117430743</v>
+        <v>117492355</v>
       </c>
       <c r="B46" t="n">
-        <v>74584</v>
+        <v>97838</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5483,30 +5499,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5514,10 +5531,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490130</v>
+        <v>490067</v>
       </c>
       <c r="R46" t="n">
-        <v>6931907</v>
+        <v>6931971</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5577,10 +5594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117430588</v>
+        <v>117492397</v>
       </c>
       <c r="B47" t="n">
-        <v>78514</v>
+        <v>79598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5589,25 +5606,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5620,10 +5637,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490018</v>
+        <v>490067</v>
       </c>
       <c r="R47" t="n">
-        <v>6931884</v>
+        <v>6931971</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5683,10 +5700,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117430632</v>
+        <v>117491116</v>
       </c>
       <c r="B48" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5695,31 +5712,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5727,10 +5743,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489989</v>
+        <v>490055</v>
       </c>
       <c r="R48" t="n">
-        <v>6931777</v>
+        <v>6931974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5790,10 +5806,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117491133</v>
+        <v>117430743</v>
       </c>
       <c r="B49" t="n">
-        <v>97836</v>
+        <v>74586</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5802,39 +5818,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5842,10 +5849,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490105</v>
+        <v>490130</v>
       </c>
       <c r="R49" t="n">
-        <v>6931938</v>
+        <v>6931907</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5905,10 +5912,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117491148</v>
+        <v>117430089</v>
       </c>
       <c r="B50" t="n">
-        <v>90464</v>
+        <v>78516</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,25 +5924,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5948,10 +5955,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490106</v>
+        <v>490039</v>
       </c>
       <c r="R50" t="n">
-        <v>6931918</v>
+        <v>6931761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6011,10 +6018,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117491096</v>
+        <v>117430485</v>
       </c>
       <c r="B51" t="n">
-        <v>79596</v>
+        <v>94242</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6027,26 +6034,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6054,10 +6062,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490055</v>
+        <v>489966</v>
       </c>
       <c r="R51" t="n">
-        <v>6931974</v>
+        <v>6931786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,10 +6125,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117430719</v>
+        <v>117492308</v>
       </c>
       <c r="B52" t="n">
-        <v>97836</v>
+        <v>78516</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6129,39 +6137,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490137</v>
+        <v>490076</v>
       </c>
       <c r="R52" t="n">
-        <v>6931927</v>
+        <v>6931894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6232,10 +6231,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117492320</v>
+        <v>117429822</v>
       </c>
       <c r="B53" t="n">
-        <v>79562</v>
+        <v>97859</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6244,30 +6243,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490085</v>
+        <v>490056</v>
       </c>
       <c r="R53" t="n">
-        <v>6931971</v>
+        <v>6931648</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117492111</v>
+        <v>117430698</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490063</v>
+        <v>489999</v>
       </c>
       <c r="R54" t="n">
-        <v>6931853</v>
+        <v>6931774</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117430698</v>
+        <v>117492111</v>
       </c>
       <c r="B55" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489999</v>
+        <v>490063</v>
       </c>
       <c r="R55" t="n">
-        <v>6931774</v>
+        <v>6931853</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -3080,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117492320</v>
+        <v>117491078</v>
       </c>
       <c r="B24" t="n">
-        <v>79564</v>
+        <v>97838</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,30 +3092,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3123,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490085</v>
+        <v>490048</v>
       </c>
       <c r="R24" t="n">
-        <v>6931971</v>
+        <v>6931976</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117491078</v>
+        <v>117492320</v>
       </c>
       <c r="B25" t="n">
-        <v>97838</v>
+        <v>79564</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3198,39 +3207,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490048</v>
+        <v>490085</v>
       </c>
       <c r="R25" t="n">
-        <v>6931976</v>
+        <v>6931971</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117491486</v>
+        <v>117491191</v>
       </c>
       <c r="B30" t="n">
-        <v>97838</v>
+        <v>79563</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3746,39 +3746,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3786,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490063</v>
+        <v>490084</v>
       </c>
       <c r="R30" t="n">
-        <v>6931903</v>
+        <v>6931897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,6 +3813,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3849,10 +3845,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117492153</v>
+        <v>117492238</v>
       </c>
       <c r="B31" t="n">
-        <v>97838</v>
+        <v>79563</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3861,39 +3857,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3901,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490067</v>
+        <v>490070</v>
       </c>
       <c r="R31" t="n">
-        <v>6931856</v>
+        <v>6931876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,6 +3924,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3964,10 +3956,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117491191</v>
+        <v>117491486</v>
       </c>
       <c r="B32" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3976,30 +3968,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4007,10 +4008,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490084</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>6931897</v>
+        <v>6931903</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,11 +4044,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växt över på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,10 +4071,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117492238</v>
+        <v>117492153</v>
       </c>
       <c r="B33" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4087,30 +4083,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4118,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490070</v>
+        <v>490067</v>
       </c>
       <c r="R33" t="n">
-        <v>6931876</v>
+        <v>6931856</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,11 +4159,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117492336</v>
+        <v>117429691</v>
       </c>
       <c r="B41" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4959,30 +4959,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4990,10 +4999,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490087</v>
+        <v>490021</v>
       </c>
       <c r="R41" t="n">
-        <v>6931968</v>
+        <v>6931639</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5053,10 +5062,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117429691</v>
+        <v>117492336</v>
       </c>
       <c r="B42" t="n">
-        <v>97838</v>
+        <v>79563</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5065,39 +5074,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490021</v>
+        <v>490087</v>
       </c>
       <c r="R42" t="n">
-        <v>6931639</v>
+        <v>6931968</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80675814</v>
+        <v>117430089</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övre Gallvattssjön, Jmt</t>
+          <t>Övre Galvattsjön , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490174.973538421</v>
+        <v>490039</v>
       </c>
       <c r="R2" t="n">
-        <v>6931634.1603684</v>
+        <v>6931761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,35 +761,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80675815</v>
+        <v>117430507</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Gallvattssjön, Jmt</t>
+          <t>Övre Galvattsjön , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490027.7927109372</v>
+        <v>490007</v>
       </c>
       <c r="R3" t="n">
-        <v>6931757.918772286</v>
+        <v>6931806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,57 +862,47 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114530260</v>
+        <v>117430588</v>
       </c>
       <c r="B4" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490272</v>
+        <v>490018</v>
       </c>
       <c r="R4" t="n">
-        <v>6931738</v>
+        <v>6931884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114530205</v>
+        <v>117492202</v>
       </c>
       <c r="B5" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490267</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>6931713</v>
+        <v>6931865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1072,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114530028</v>
+        <v>117492308</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490320</v>
+        <v>490076</v>
       </c>
       <c r="R6" t="n">
-        <v>6931637</v>
+        <v>6931894</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,22 +1173,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114530108</v>
+        <v>117430743</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,31 +1191,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490302</v>
+        <v>490130</v>
       </c>
       <c r="R7" t="n">
-        <v>6931661</v>
+        <v>6931907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,12 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,6 +1262,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1339,44 +1274,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114530231</v>
+        <v>114530260</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490267</v>
+        <v>490272</v>
       </c>
       <c r="R8" t="n">
-        <v>6931713</v>
+        <v>6931738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114530062</v>
+        <v>80675815</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,14 +1416,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Galvattsjön , Jmt</t>
+          <t>Övre Gallvattssjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490320</v>
+        <v>490028</v>
       </c>
       <c r="R9" t="n">
-        <v>6931637</v>
+        <v>6931758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,12 +1450,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2019-07-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2019-07-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,30 +1468,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114530149</v>
+        <v>117492320</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490291</v>
+        <v>490085</v>
       </c>
       <c r="R10" t="n">
-        <v>6931700</v>
+        <v>6931971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,17 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer på björk, gran och asp</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,22 +1582,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114530290</v>
+        <v>117492369</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,31 +1600,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1717,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490305</v>
+        <v>490067</v>
       </c>
       <c r="R11" t="n">
-        <v>6931785</v>
+        <v>6931971</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,12 +1657,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,6 +1671,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1772,49 +1683,45 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114530178</v>
+        <v>117429793</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1822,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490303</v>
+        <v>490021</v>
       </c>
       <c r="R12" t="n">
-        <v>6931709</v>
+        <v>6931643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,17 +1759,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer i stort sett överallt</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,54 +1785,45 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114530093</v>
+        <v>117430485</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1938,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490307</v>
+        <v>489966</v>
       </c>
       <c r="R13" t="n">
-        <v>6931645</v>
+        <v>6931786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,12 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,6 +1875,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1993,58 +1887,44 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117430139</v>
+        <v>117491148</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2052,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490013</v>
+        <v>490106</v>
       </c>
       <c r="R14" t="n">
-        <v>6931777</v>
+        <v>6931918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,39 +1988,34 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117491096</v>
+        <v>114530062</v>
       </c>
       <c r="B15" t="n">
-        <v>79598</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2158,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490055</v>
+        <v>490320</v>
       </c>
       <c r="R15" t="n">
-        <v>6931974</v>
+        <v>6931637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,44 +2089,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117492484</v>
+        <v>114530178</v>
       </c>
       <c r="B16" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490068</v>
+        <v>490303</v>
       </c>
       <c r="R16" t="n">
-        <v>6931975</v>
+        <v>6931709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,12 +2164,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer i stort sett överallt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,44 +2195,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117491116</v>
+        <v>114530231</v>
       </c>
       <c r="B17" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490055</v>
+        <v>490267</v>
       </c>
       <c r="R17" t="n">
-        <v>6931974</v>
+        <v>6931713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,12 +2270,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,22 +2296,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117492153</v>
+        <v>114530320</v>
       </c>
       <c r="B18" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,35 +2314,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2485,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490067</v>
+        <v>490327</v>
       </c>
       <c r="R18" t="n">
-        <v>6931856</v>
+        <v>6931760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,12 +2371,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,22 +2397,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117430507</v>
+        <v>114530028</v>
       </c>
       <c r="B19" t="n">
-        <v>78516</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2591,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490007</v>
+        <v>490320</v>
       </c>
       <c r="R19" t="n">
-        <v>6931806</v>
+        <v>6931637</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,12 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,44 +2498,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117492397</v>
+        <v>114530149</v>
       </c>
       <c r="B20" t="n">
-        <v>79598</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2697,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490067</v>
+        <v>490291</v>
       </c>
       <c r="R20" t="n">
-        <v>6931971</v>
+        <v>6931700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,12 +2573,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växer på björk, gran och asp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,22 +2604,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117492202</v>
+        <v>114530205</v>
       </c>
       <c r="B21" t="n">
-        <v>78516</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,21 +2622,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2803,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490061</v>
+        <v>490267</v>
       </c>
       <c r="R21" t="n">
-        <v>6931865</v>
+        <v>6931713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,12 +2679,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,22 +2705,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117492308</v>
+        <v>114530377</v>
       </c>
       <c r="B22" t="n">
-        <v>78516</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,21 +2723,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2909,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490076</v>
+        <v>490327</v>
       </c>
       <c r="R22" t="n">
-        <v>6931894</v>
+        <v>6931760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2939,12 +2780,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,22 +2806,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117430608</v>
+        <v>117429852</v>
       </c>
       <c r="B23" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,21 +2824,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3015,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489984</v>
+        <v>490056</v>
       </c>
       <c r="R23" t="n">
-        <v>6931792</v>
+        <v>6931671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,58 +2907,44 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117430719</v>
+        <v>117430114</v>
       </c>
       <c r="B24" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3130,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490137</v>
+        <v>490047</v>
       </c>
       <c r="R24" t="n">
-        <v>6931927</v>
+        <v>6931770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,22 +3008,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117430743</v>
+        <v>117430408</v>
       </c>
       <c r="B25" t="n">
-        <v>74586</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,21 +3026,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3236,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490130</v>
+        <v>490012</v>
       </c>
       <c r="R25" t="n">
-        <v>6931907</v>
+        <v>6931800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3274,6 +3091,11 @@
           <t>2024-05-31</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3292,58 +3114,44 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117491486</v>
+        <v>117430730</v>
       </c>
       <c r="B26" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3351,10 +3159,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490063</v>
+        <v>490132</v>
       </c>
       <c r="R26" t="n">
-        <v>6931903</v>
+        <v>6931915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3407,22 +3215,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117492320</v>
+        <v>117430761</v>
       </c>
       <c r="B27" t="n">
-        <v>79564</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490085</v>
+        <v>490117</v>
       </c>
       <c r="R27" t="n">
-        <v>6931971</v>
+        <v>6931912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3513,50 +3316,44 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117430485</v>
+        <v>117491116</v>
       </c>
       <c r="B28" t="n">
-        <v>94242</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3564,10 +3361,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489966</v>
+        <v>490055</v>
       </c>
       <c r="R28" t="n">
-        <v>6931786</v>
+        <v>6931974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3620,58 +3417,44 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117491078</v>
+        <v>117491191</v>
       </c>
       <c r="B29" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3679,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490048</v>
+        <v>490084</v>
       </c>
       <c r="R29" t="n">
-        <v>6931976</v>
+        <v>6931897</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3717,6 +3500,11 @@
           <t>2024-05-31</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växt över på gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3735,22 +3523,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117429852</v>
+        <v>117491453</v>
       </c>
       <c r="B30" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,10 +3568,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490056</v>
+        <v>490096</v>
       </c>
       <c r="R30" t="n">
-        <v>6931671</v>
+        <v>6931958</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3841,22 +3624,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117430588</v>
+        <v>117492238</v>
       </c>
       <c r="B31" t="n">
-        <v>78516</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,21 +3642,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3891,10 +3669,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490018</v>
+        <v>490070</v>
       </c>
       <c r="R31" t="n">
-        <v>6931884</v>
+        <v>6931876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,6 +3707,11 @@
           <t>2024-05-31</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3947,22 +3730,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117430730</v>
+        <v>117492336</v>
       </c>
       <c r="B32" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490132</v>
+        <v>490087</v>
       </c>
       <c r="R32" t="n">
-        <v>6931915</v>
+        <v>6931968</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,22 +3831,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117491191</v>
+        <v>117492484</v>
       </c>
       <c r="B33" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4103,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490084</v>
+        <v>490068</v>
       </c>
       <c r="R33" t="n">
-        <v>6931897</v>
+        <v>6931975</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4141,11 +3914,6 @@
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växt över på gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4164,44 +3932,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117430114</v>
+        <v>117430056</v>
       </c>
       <c r="B34" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4214,10 +3977,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490047</v>
+        <v>490061</v>
       </c>
       <c r="R34" t="n">
-        <v>6931770</v>
+        <v>6931684</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,22 +4033,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117430446</v>
+        <v>117491096</v>
       </c>
       <c r="B35" t="n">
-        <v>104916</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,27 +4051,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4321,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489965</v>
+        <v>490055</v>
       </c>
       <c r="R35" t="n">
-        <v>6931782</v>
+        <v>6931974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4377,44 +4134,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117492238</v>
+        <v>117492397</v>
       </c>
       <c r="B36" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4427,10 +4179,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490070</v>
+        <v>490067</v>
       </c>
       <c r="R36" t="n">
-        <v>6931876</v>
+        <v>6931971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4465,11 +4217,6 @@
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4488,22 +4235,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117430408</v>
+        <v>114530093</v>
       </c>
       <c r="B37" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4511,26 +4253,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4538,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490012</v>
+        <v>490307</v>
       </c>
       <c r="R37" t="n">
-        <v>6931800</v>
+        <v>6931645</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4568,17 +4315,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4587,7 +4329,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4599,22 +4340,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117492369</v>
+        <v>114530108</v>
       </c>
       <c r="B38" t="n">
-        <v>79564</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,26 +4358,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4649,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490067</v>
+        <v>490302</v>
       </c>
       <c r="R38" t="n">
-        <v>6931971</v>
+        <v>6931661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,12 +4420,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4693,7 +4434,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4705,50 +4445,49 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117430632</v>
+        <v>114530290</v>
       </c>
       <c r="B39" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4756,10 +4495,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489989</v>
+        <v>490305</v>
       </c>
       <c r="R39" t="n">
-        <v>6931777</v>
+        <v>6931785</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4786,12 +4525,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4800,7 +4539,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4812,22 +4550,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117492336</v>
+        <v>117430698</v>
       </c>
       <c r="B40" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4835,26 +4568,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4862,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490087</v>
+        <v>489999</v>
       </c>
       <c r="R40" t="n">
-        <v>6931968</v>
+        <v>6931774</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4906,7 +4644,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4918,50 +4655,49 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117492355</v>
+        <v>117492111</v>
       </c>
       <c r="B41" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4969,10 +4705,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490067</v>
+        <v>490063</v>
       </c>
       <c r="R41" t="n">
-        <v>6931971</v>
+        <v>6931853</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5013,7 +4749,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5025,22 +4760,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117491133</v>
+        <v>117429691</v>
       </c>
       <c r="B42" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +4797,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5084,10 +4814,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490105</v>
+        <v>490021</v>
       </c>
       <c r="R42" t="n">
-        <v>6931938</v>
+        <v>6931639</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5140,49 +4870,53 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117430056</v>
+        <v>117430139</v>
       </c>
       <c r="B43" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5190,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490061</v>
+        <v>490013</v>
       </c>
       <c r="R43" t="n">
-        <v>6931684</v>
+        <v>6931777</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5246,22 +4980,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117429691</v>
+        <v>117430545</v>
       </c>
       <c r="B44" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,14 +5017,10 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5305,10 +5030,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490021</v>
+        <v>490044</v>
       </c>
       <c r="R44" t="n">
-        <v>6931639</v>
+        <v>6931836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5361,49 +5086,53 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117491148</v>
+        <v>117430719</v>
       </c>
       <c r="B45" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5411,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490106</v>
+        <v>490137</v>
       </c>
       <c r="R45" t="n">
-        <v>6931918</v>
+        <v>6931927</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,22 +5196,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117430545</v>
+        <v>117491078</v>
       </c>
       <c r="B46" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,10 +5233,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5522,10 +5250,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490044</v>
+        <v>490048</v>
       </c>
       <c r="R46" t="n">
-        <v>6931836</v>
+        <v>6931976</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5578,49 +5306,53 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117491453</v>
+        <v>117491133</v>
       </c>
       <c r="B47" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5628,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490096</v>
+        <v>490105</v>
       </c>
       <c r="R47" t="n">
-        <v>6931958</v>
+        <v>6931938</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5684,49 +5416,53 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117430040</v>
+        <v>117491486</v>
       </c>
       <c r="B48" t="n">
-        <v>79523</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5734,10 +5470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490060</v>
+        <v>490063</v>
       </c>
       <c r="R48" t="n">
-        <v>6931682</v>
+        <v>6931903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5790,22 +5526,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117492257</v>
+        <v>117492153</v>
       </c>
       <c r="B49" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5832,7 +5563,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5849,10 +5580,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490070</v>
+        <v>490067</v>
       </c>
       <c r="R49" t="n">
-        <v>6931897</v>
+        <v>6931856</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5905,49 +5636,53 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117430761</v>
+        <v>117492257</v>
       </c>
       <c r="B50" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5955,10 +5690,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490117</v>
+        <v>490070</v>
       </c>
       <c r="R50" t="n">
-        <v>6931912</v>
+        <v>6931897</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6011,44 +5746,39 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117429822</v>
+        <v>117492355</v>
       </c>
       <c r="B51" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6062,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490056</v>
+        <v>490067</v>
       </c>
       <c r="R51" t="n">
-        <v>6931648</v>
+        <v>6931971</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6118,49 +5848,45 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117430089</v>
+        <v>117430446</v>
       </c>
       <c r="B52" t="n">
-        <v>78516</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>221725</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6168,10 +5894,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490039</v>
+        <v>489965</v>
       </c>
       <c r="R52" t="n">
-        <v>6931761</v>
+        <v>6931782</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6224,22 +5950,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117429793</v>
+        <v>80675814</v>
       </c>
       <c r="B53" t="n">
-        <v>94242</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6247,21 +5968,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2809</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6271,14 +5992,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Övre Galvattsjön , Jmt</t>
+          <t>Övre Gallvattssjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490021</v>
+        <v>490175</v>
       </c>
       <c r="R53" t="n">
-        <v>6931643</v>
+        <v>6931634</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6305,12 +6026,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2019-07-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2019-07-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6323,62 +6044,58 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117492111</v>
+        <v>117429822</v>
       </c>
       <c r="B54" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6386,10 +6103,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490063</v>
+        <v>490056</v>
       </c>
       <c r="R54" t="n">
-        <v>6931853</v>
+        <v>6931648</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6430,6 +6147,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6441,54 +6159,45 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117430698</v>
+        <v>117430632</v>
       </c>
       <c r="B55" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6496,10 +6205,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489999</v>
+        <v>489989</v>
       </c>
       <c r="R55" t="n">
-        <v>6931774</v>
+        <v>6931777</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6540,6 +6249,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6551,10 +6261,111 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117430040</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Övre Galvattsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>490060</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6931682</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56201-2021 artfynd.xlsx
+++ b/artfynd/A 56201-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430507</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430588</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492202</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492308</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492320</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492369</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117429793</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430485</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491148</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530062</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2199,6 +2274,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530178</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2300,6 +2380,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530231</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530320</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530028</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2608,6 +2703,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530149</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,6 +2809,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530205</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530377</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117429852</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430114</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3118,6 +3238,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430408</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3219,6 +3344,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430730</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3320,6 +3450,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430761</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491116</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491191</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3628,6 +3773,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491453</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3734,6 +3884,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492238</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3835,6 +3990,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492336</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492484</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4037,6 +4202,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430056</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4138,6 +4308,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491096</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4239,6 +4414,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492397</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530093</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4449,6 +4634,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530108</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4554,6 +4744,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530290</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4659,6 +4854,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430698</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4764,6 +4964,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492111</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4874,6 +5079,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117429691</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4984,6 +5194,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430139</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5090,6 +5305,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430545</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5200,6 +5420,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430719</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5310,6 +5535,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491078</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5420,6 +5650,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491133</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5530,6 +5765,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117491486</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5640,6 +5880,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492153</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5750,6 +5995,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492257</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5852,6 +6102,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117492355</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5954,6 +6209,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430446</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6061,6 +6321,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675814</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6163,6 +6428,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117429822</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6265,6 +6535,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430632</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6366,8 +6641,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117430040</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>